--- a/data/Population_bg_2009_2024.xlsx
+++ b/data/Population_bg_2009_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/3.PC/Data_Science/12.Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_AD4DF75460589B3ACB728432C71D4FCA5ADEDD97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C686A2-F75C-44B6-BD88-62C91A610591}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_AD4DF75460589B3ACB728432C71D4FCA5ADEDD97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6B96A6C-5415-4C22-9989-506F87117FF4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,10 +38,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">Year </t>
+    <t>Total</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -388,10 +388,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
